--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92538968208</v>
+        <v>46157.93112571101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112571101</v>
+        <v>46157.93367546731</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93367546731</v>
+        <v>46157.9367061386</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9367061386</v>
+        <v>46158.2819351885</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2819351885</v>
+        <v>46158.29716725061</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29716725061</v>
+        <v>46158.29789463968</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29789463968</v>
+        <v>46158.33355190849</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355190849</v>
+        <v>46158.3721031064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3721031064</v>
+        <v>46158.37267367628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
